--- a/workbook-template/Service-Tracker-Template.xlsx
+++ b/workbook-template/Service-Tracker-Template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="116">
   <si>
     <t xml:space="preserve">Service Tracker — how this workbook works</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">  •  Opportunity was rarely filled in on the old tabs, which is why Pen% showed a divide-by-zero error — Advisor Daily asks for Opportunity and Sold on every row, so Pen% always has something to divide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  •  Tyres Possible/Sold are counts (e.g. 4 possible, 2 sold on one visit), not a Y/N flag like the other categories — a single vehicle can take more than one tyre.</t>
   </si>
   <si>
     <t xml:space="preserve">  •  The old Service Plans log (264 rows back to 2023, under advisor names Abbie/Pete/Rhi/Sam that don't match the current team) was not migrated automatically — those names don't map cleanly onto the current roster. It's preserved untouched in the original file if you need to look something up; copy rows across by hand if any are still relevant.</t>
@@ -159,11 +162,11 @@
   </si>
   <si>
     <t xml:space="preserve">Tyres
-Opportunity</t>
+Possible (count)</t>
   </si>
   <si>
     <t xml:space="preserve">Tyres
-Sold</t>
+Sold (count)</t>
   </si>
   <si>
     <t xml:space="preserve">Geometry
@@ -302,6 +305,12 @@
   </si>
   <si>
     <t xml:space="preserve">Carried over from the old Standards tab, TGT 85%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales per visit target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add-ons sold (tyres + geometry + A/C + fuel treatment + service plans) per retail visit.</t>
   </si>
   <si>
     <t xml:space="preserve">Advisor Monthly Summary</t>
@@ -871,7 +880,7 @@
     <tabColor rgb="FF6B7280"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -967,32 +976,37 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1020,13 +1034,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
@@ -1037,10 +1051,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1052,10 +1066,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1067,10 +1081,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1082,45 +1096,45 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1165,52 +1179,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1218,49 +1232,49 @@
         <v>46204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="O2" s="9" t="n">
         <v>95</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19264,10 +19278,14 @@
       <c r="P1002" s="11"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E3:N1002 P3:P1002" type="list">
+  <dataValidations count="4">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G3:N1002 P3:P1002" type="list">
       <formula1>"Y,N"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Enter a count of tyres (0-4)" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E3:F1002" type="whole">
+      <formula1>0</formula1>
+      <formula2>4</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B3:B1002" type="list">
       <formula1>'Lookup Lists'!$A$2:$A$30</formula1>
@@ -19305,19 +19323,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19325,7 +19343,7 @@
         <v>46204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>7.5</v>
@@ -26372,22 +26390,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="E1" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26395,19 +26413,19 @@
         <v>46204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34448,16 +34466,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34465,13 +34483,13 @@
         <v>46204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40497,7 +40515,7 @@
     <tabColor rgb="FFB77900"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -40507,112 +40525,123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="14" t="n">
         <v>65665</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="14" t="n">
         <v>28500</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>90</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>25</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -40641,78 +40670,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40720,18 +40749,18 @@
         <v>46023</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B3,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A3,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A3,0))</f>
         <v>0</v>
       </c>
       <c r="D3" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B3,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A3,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A3,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B3,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A3,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A3,0))</f>
         <v>0</v>
       </c>
       <c r="E3" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B3,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A3,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A3,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B3,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A3,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A3,0))</f>
         <v>0</v>
       </c>
       <c r="F3" s="20" t="n">
@@ -40812,18 +40841,18 @@
         <v>46023</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B4,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A4,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A4,0))</f>
         <v>0</v>
       </c>
       <c r="D4" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B4,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A4,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A4,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B4,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A4,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A4,0))</f>
         <v>0</v>
       </c>
       <c r="E4" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B4,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A4,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A4,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B4,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A4,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A4,0))</f>
         <v>0</v>
       </c>
       <c r="F4" s="20" t="n">
@@ -40904,18 +40933,18 @@
         <v>46023</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B5,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A5,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A5,0))</f>
         <v>0</v>
       </c>
       <c r="D5" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B5,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A5,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A5,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B5,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A5,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A5,0))</f>
         <v>0</v>
       </c>
       <c r="E5" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B5,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A5,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A5,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B5,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A5,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A5,0))</f>
         <v>0</v>
       </c>
       <c r="F5" s="20" t="n">
@@ -40996,18 +41025,18 @@
         <v>46023</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B6,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A6,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A6,0))</f>
         <v>0</v>
       </c>
       <c r="D6" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B6,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A6,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A6,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B6,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A6,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A6,0))</f>
         <v>0</v>
       </c>
       <c r="E6" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B6,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A6,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A6,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B6,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A6,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A6,0))</f>
         <v>0</v>
       </c>
       <c r="F6" s="20" t="n">
@@ -41088,18 +41117,18 @@
         <v>46054</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B7,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A7,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A7,0))</f>
         <v>0</v>
       </c>
       <c r="D7" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B7,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A7,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A7,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B7,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A7,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A7,0))</f>
         <v>0</v>
       </c>
       <c r="E7" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B7,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A7,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A7,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B7,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A7,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A7,0))</f>
         <v>0</v>
       </c>
       <c r="F7" s="20" t="n">
@@ -41180,18 +41209,18 @@
         <v>46054</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B8,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A8,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A8,0))</f>
         <v>0</v>
       </c>
       <c r="D8" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B8,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A8,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A8,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B8,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A8,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A8,0))</f>
         <v>0</v>
       </c>
       <c r="E8" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B8,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A8,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A8,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B8,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A8,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A8,0))</f>
         <v>0</v>
       </c>
       <c r="F8" s="20" t="n">
@@ -41272,18 +41301,18 @@
         <v>46054</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B9,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A9,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="D9" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B9,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A9,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A9,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B9,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A9,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="E9" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B9,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A9,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A9,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B9,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A9,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="F9" s="20" t="n">
@@ -41364,18 +41393,18 @@
         <v>46054</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B10,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A10,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="D10" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B10,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A10,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A10,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B10,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A10,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="E10" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B10,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A10,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A10,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B10,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A10,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="F10" s="20" t="n">
@@ -41456,18 +41485,18 @@
         <v>46082</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B11,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A11,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="D11" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B11,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A11,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A11,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B11,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A11,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="E11" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B11,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A11,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A11,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B11,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A11,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="F11" s="20" t="n">
@@ -41548,18 +41577,18 @@
         <v>46082</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B12,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A12,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="D12" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B12,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A12,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A12,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B12,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A12,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="E12" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B12,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A12,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A12,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B12,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A12,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="F12" s="20" t="n">
@@ -41640,18 +41669,18 @@
         <v>46082</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B13,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A13,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="D13" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B13,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A13,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A13,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B13,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A13,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="E13" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B13,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A13,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A13,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B13,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A13,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="F13" s="20" t="n">
@@ -41732,18 +41761,18 @@
         <v>46082</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B14,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A14,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="D14" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B14,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A14,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A14,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B14,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A14,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="E14" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B14,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A14,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A14,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B14,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A14,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="F14" s="20" t="n">
@@ -41824,18 +41853,18 @@
         <v>46113</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B15,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A15,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="D15" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B15,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A15,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A15,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B15,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A15,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="E15" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B15,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A15,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A15,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B15,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A15,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="F15" s="20" t="n">
@@ -41916,18 +41945,18 @@
         <v>46113</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B16,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A16,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="D16" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B16,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A16,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A16,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B16,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A16,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="E16" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B16,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A16,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A16,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B16,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A16,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="F16" s="20" t="n">
@@ -42008,18 +42037,18 @@
         <v>46113</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B17,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A17,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="D17" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B17,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A17,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A17,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B17,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A17,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="E17" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B17,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A17,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A17,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B17,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A17,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="F17" s="20" t="n">
@@ -42100,18 +42129,18 @@
         <v>46113</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B18,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A18,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="D18" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B18,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A18,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A18,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B18,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A18,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="E18" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B18,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A18,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A18,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B18,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A18,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="F18" s="20" t="n">
@@ -42192,18 +42221,18 @@
         <v>46143</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B19,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A19,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="D19" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B19,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A19,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A19,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B19,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A19,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="E19" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B19,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A19,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A19,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B19,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A19,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="F19" s="20" t="n">
@@ -42284,18 +42313,18 @@
         <v>46143</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B20,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A20,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="D20" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B20,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A20,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A20,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B20,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A20,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="E20" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B20,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A20,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A20,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B20,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A20,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="F20" s="20" t="n">
@@ -42376,18 +42405,18 @@
         <v>46143</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B21,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A21,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="D21" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B21,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A21,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A21,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B21,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A21,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="E21" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B21,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A21,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A21,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B21,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A21,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="F21" s="20" t="n">
@@ -42468,18 +42497,18 @@
         <v>46143</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B22,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A22,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="D22" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B22,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A22,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A22,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B22,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A22,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="E22" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B22,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A22,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A22,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B22,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A22,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="F22" s="20" t="n">
@@ -42560,18 +42589,18 @@
         <v>46174</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B23,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A23,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="D23" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B23,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A23,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A23,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B23,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A23,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="E23" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B23,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A23,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A23,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B23,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A23,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="F23" s="20" t="n">
@@ -42652,18 +42681,18 @@
         <v>46174</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B24,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A24,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="D24" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B24,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A24,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A24,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B24,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A24,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="E24" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B24,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A24,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A24,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B24,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A24,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="F24" s="20" t="n">
@@ -42744,18 +42773,18 @@
         <v>46174</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B25,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A25,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="D25" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B25,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A25,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A25,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B25,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A25,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="E25" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B25,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A25,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A25,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B25,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A25,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="F25" s="20" t="n">
@@ -42836,18 +42865,18 @@
         <v>46174</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C26" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B26,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A26,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="D26" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B26,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A26,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A26,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B26,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A26,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="E26" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B26,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A26,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A26,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B26,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A26,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="F26" s="20" t="n">
@@ -42928,18 +42957,18 @@
         <v>46204</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B27,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A27,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="D27" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B27,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A27,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A27,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B27,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A27,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="E27" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B27,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A27,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A27,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B27,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A27,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="F27" s="20" t="n">
@@ -43020,18 +43049,18 @@
         <v>46204</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B28,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A28,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="D28" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B28,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A28,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A28,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B28,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A28,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="E28" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B28,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A28,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A28,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B28,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A28,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="F28" s="20" t="n">
@@ -43112,18 +43141,18 @@
         <v>46204</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B29,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A29,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="D29" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B29,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A29,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A29,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B29,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A29,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="E29" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B29,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A29,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A29,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B29,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A29,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="F29" s="20" t="n">
@@ -43204,18 +43233,18 @@
         <v>46204</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B30,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A30,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="D30" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B30,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A30,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A30,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B30,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A30,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="E30" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B30,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A30,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A30,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B30,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A30,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="F30" s="20" t="n">
@@ -43296,18 +43325,18 @@
         <v>46235</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B31,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A31,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="D31" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B31,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A31,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A31,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B31,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A31,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="E31" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B31,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A31,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A31,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B31,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A31,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="F31" s="20" t="n">
@@ -43388,18 +43417,18 @@
         <v>46235</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B32,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A32,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="D32" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B32,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A32,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A32,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B32,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A32,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="E32" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B32,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A32,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A32,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B32,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A32,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="F32" s="20" t="n">
@@ -43480,18 +43509,18 @@
         <v>46235</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B33,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A33,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="D33" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B33,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A33,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A33,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B33,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A33,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="E33" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B33,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A33,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A33,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B33,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A33,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="F33" s="20" t="n">
@@ -43572,18 +43601,18 @@
         <v>46235</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C34" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B34,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A34,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="D34" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B34,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A34,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A34,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B34,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A34,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="E34" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B34,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A34,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A34,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B34,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A34,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="F34" s="20" t="n">
@@ -43664,18 +43693,18 @@
         <v>46266</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B35,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A35,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="D35" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B35,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A35,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A35,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B35,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A35,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="E35" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B35,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A35,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A35,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B35,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A35,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="F35" s="20" t="n">
@@ -43756,18 +43785,18 @@
         <v>46266</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B36,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A36,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="D36" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B36,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A36,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A36,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B36,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A36,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B36,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A36,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A36,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B36,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A36,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="F36" s="20" t="n">
@@ -43848,18 +43877,18 @@
         <v>46266</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C37" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B37,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A37,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="D37" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B37,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A37,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A37,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B37,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A37,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="E37" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B37,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A37,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A37,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B37,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A37,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="F37" s="20" t="n">
@@ -43940,18 +43969,18 @@
         <v>46266</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B38,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A38,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="D38" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B38,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A38,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A38,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B38,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A38,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="E38" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B38,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A38,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A38,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B38,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A38,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="F38" s="20" t="n">
@@ -44032,18 +44061,18 @@
         <v>46296</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B39,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A39,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="D39" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B39,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A39,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A39,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B39,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A39,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="E39" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B39,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A39,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A39,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B39,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A39,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="F39" s="20" t="n">
@@ -44124,18 +44153,18 @@
         <v>46296</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B40,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A40,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="D40" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B40,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A40,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A40,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B40,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A40,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="E40" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B40,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A40,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A40,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B40,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A40,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="F40" s="20" t="n">
@@ -44216,18 +44245,18 @@
         <v>46296</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B41,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A41,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="D41" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B41,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A41,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A41,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B41,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A41,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="E41" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B41,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A41,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A41,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B41,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A41,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="F41" s="20" t="n">
@@ -44308,18 +44337,18 @@
         <v>46296</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C42" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B42,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A42,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="D42" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B42,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A42,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A42,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B42,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A42,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="E42" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B42,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A42,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A42,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B42,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A42,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="F42" s="20" t="n">
@@ -44400,18 +44429,18 @@
         <v>46327</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B43,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A43,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="D43" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B43,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A43,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A43,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B43,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A43,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="E43" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B43,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A43,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A43,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B43,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A43,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="F43" s="20" t="n">
@@ -44492,18 +44521,18 @@
         <v>46327</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B44,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A44,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="D44" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B44,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A44,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A44,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B44,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A44,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="E44" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B44,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A44,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A44,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B44,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A44,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="F44" s="20" t="n">
@@ -44584,18 +44613,18 @@
         <v>46327</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C45" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B45,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A45,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A45,0))</f>
         <v>0</v>
       </c>
       <c r="D45" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B45,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A45,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A45,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B45,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A45,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A45,0))</f>
         <v>0</v>
       </c>
       <c r="E45" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B45,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A45,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A45,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B45,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A45,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A45,0))</f>
         <v>0</v>
       </c>
       <c r="F45" s="20" t="n">
@@ -44676,18 +44705,18 @@
         <v>46327</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C46" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B46,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A46,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A46,0))</f>
         <v>0</v>
       </c>
       <c r="D46" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B46,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A46,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A46,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B46,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A46,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A46,0))</f>
         <v>0</v>
       </c>
       <c r="E46" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B46,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A46,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A46,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B46,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A46,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A46,0))</f>
         <v>0</v>
       </c>
       <c r="F46" s="20" t="n">
@@ -44768,18 +44797,18 @@
         <v>46357</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B47,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A47,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A47,0))</f>
         <v>0</v>
       </c>
       <c r="D47" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B47,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A47,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A47,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B47,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A47,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A47,0))</f>
         <v>0</v>
       </c>
       <c r="E47" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B47,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A47,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A47,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B47,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A47,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A47,0))</f>
         <v>0</v>
       </c>
       <c r="F47" s="20" t="n">
@@ -44860,18 +44889,18 @@
         <v>46357</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B48,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A48,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A48,0))</f>
         <v>0</v>
       </c>
       <c r="D48" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B48,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A48,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A48,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B48,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A48,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A48,0))</f>
         <v>0</v>
       </c>
       <c r="E48" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B48,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A48,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A48,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B48,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A48,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A48,0))</f>
         <v>0</v>
       </c>
       <c r="F48" s="20" t="n">
@@ -44952,18 +44981,18 @@
         <v>46357</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C49" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B49,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A49,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A49,0))</f>
         <v>0</v>
       </c>
       <c r="D49" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B49,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A49,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A49,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B49,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A49,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A49,0))</f>
         <v>0</v>
       </c>
       <c r="E49" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B49,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A49,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A49,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B49,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A49,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A49,0))</f>
         <v>0</v>
       </c>
       <c r="F49" s="20" t="n">
@@ -45044,18 +45073,18 @@
         <v>46357</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C50" s="19" t="n">
         <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B50,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A50,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A50,0))</f>
         <v>0</v>
       </c>
       <c r="D50" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B50,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A50,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A50,0),'Advisor Daily'!$E$3:$E$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$E$3:$E$3001,'Advisor Daily'!$B$3:$B$3001,$B50,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A50,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A50,0))</f>
         <v>0</v>
       </c>
       <c r="E50" s="19" t="n">
-        <f aca="false">COUNTIFS('Advisor Daily'!$B$3:$B$3001,$B50,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A50,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A50,0),'Advisor Daily'!$F$3:$F$3001,"Y")</f>
+        <f aca="false">SUMIFS('Advisor Daily'!$F$3:$F$3001,'Advisor Daily'!$B$3:$B$3001,$B50,'Advisor Daily'!$A$3:$A$3001,"&gt;="&amp;$A50,'Advisor Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A50,0))</f>
         <v>0</v>
       </c>
       <c r="F50" s="20" t="n">
@@ -45133,27 +45162,27 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45161,7 +45190,7 @@
         <v>46023</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C54" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B54,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A54,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A54,0))</f>
@@ -45185,7 +45214,7 @@
         <v>46023</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C55" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B55,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A55,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A55,0))</f>
@@ -45209,7 +45238,7 @@
         <v>46023</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C56" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B56,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A56,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A56,0))</f>
@@ -45233,7 +45262,7 @@
         <v>46023</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C57" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B57,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A57,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A57,0))</f>
@@ -45257,7 +45286,7 @@
         <v>46023</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C58" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B58,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A58,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A58,0))</f>
@@ -45281,7 +45310,7 @@
         <v>46023</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B59,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A59,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A59,0))</f>
@@ -45305,7 +45334,7 @@
         <v>46023</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C60" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B60,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A60,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A60,0))</f>
@@ -45329,7 +45358,7 @@
         <v>46023</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C61" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B61,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A61,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A61,0))</f>
@@ -45353,7 +45382,7 @@
         <v>46023</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C62" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B62,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A62,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A62,0))</f>
@@ -45377,7 +45406,7 @@
         <v>46023</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C63" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B63,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A63,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A63,0))</f>
@@ -45401,7 +45430,7 @@
         <v>46023</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C64" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B64,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A64,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A64,0))</f>
@@ -45425,7 +45454,7 @@
         <v>46054</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C65" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B65,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A65,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A65,0))</f>
@@ -45449,7 +45478,7 @@
         <v>46054</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C66" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B66,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A66,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A66,0))</f>
@@ -45473,7 +45502,7 @@
         <v>46054</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C67" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B67,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A67,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A67,0))</f>
@@ -45497,7 +45526,7 @@
         <v>46054</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C68" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B68,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A68,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A68,0))</f>
@@ -45521,7 +45550,7 @@
         <v>46054</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C69" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B69,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A69,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A69,0))</f>
@@ -45545,7 +45574,7 @@
         <v>46054</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C70" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B70,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A70,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A70,0))</f>
@@ -45569,7 +45598,7 @@
         <v>46054</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C71" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B71,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A71,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A71,0))</f>
@@ -45593,7 +45622,7 @@
         <v>46054</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C72" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B72,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A72,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A72,0))</f>
@@ -45617,7 +45646,7 @@
         <v>46054</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C73" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B73,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A73,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A73,0))</f>
@@ -45641,7 +45670,7 @@
         <v>46054</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C74" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B74,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A74,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A74,0))</f>
@@ -45665,7 +45694,7 @@
         <v>46054</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C75" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B75,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A75,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A75,0))</f>
@@ -45689,7 +45718,7 @@
         <v>46082</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C76" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B76,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A76,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A76,0))</f>
@@ -45713,7 +45742,7 @@
         <v>46082</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C77" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B77,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A77,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A77,0))</f>
@@ -45737,7 +45766,7 @@
         <v>46082</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C78" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B78,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A78,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A78,0))</f>
@@ -45761,7 +45790,7 @@
         <v>46082</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C79" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B79,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A79,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A79,0))</f>
@@ -45785,7 +45814,7 @@
         <v>46082</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C80" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B80,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A80,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A80,0))</f>
@@ -45809,7 +45838,7 @@
         <v>46082</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C81" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B81,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A81,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A81,0))</f>
@@ -45833,7 +45862,7 @@
         <v>46082</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C82" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B82,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A82,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A82,0))</f>
@@ -45857,7 +45886,7 @@
         <v>46082</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C83" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B83,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A83,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A83,0))</f>
@@ -45881,7 +45910,7 @@
         <v>46082</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C84" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B84,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A84,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A84,0))</f>
@@ -45905,7 +45934,7 @@
         <v>46082</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C85" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B85,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A85,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A85,0))</f>
@@ -45929,7 +45958,7 @@
         <v>46082</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C86" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B86,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A86,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A86,0))</f>
@@ -45953,7 +45982,7 @@
         <v>46113</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C87" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B87,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A87,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A87,0))</f>
@@ -45977,7 +46006,7 @@
         <v>46113</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C88" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B88,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A88,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A88,0))</f>
@@ -46001,7 +46030,7 @@
         <v>46113</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C89" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B89,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A89,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A89,0))</f>
@@ -46025,7 +46054,7 @@
         <v>46113</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C90" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B90,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A90,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A90,0))</f>
@@ -46049,7 +46078,7 @@
         <v>46113</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C91" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B91,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A91,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A91,0))</f>
@@ -46073,7 +46102,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C92" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B92,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A92,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A92,0))</f>
@@ -46097,7 +46126,7 @@
         <v>46113</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C93" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B93,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A93,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A93,0))</f>
@@ -46121,7 +46150,7 @@
         <v>46113</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C94" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B94,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A94,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A94,0))</f>
@@ -46145,7 +46174,7 @@
         <v>46113</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C95" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B95,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A95,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A95,0))</f>
@@ -46169,7 +46198,7 @@
         <v>46113</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C96" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B96,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A96,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A96,0))</f>
@@ -46193,7 +46222,7 @@
         <v>46113</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C97" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B97,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A97,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A97,0))</f>
@@ -46217,7 +46246,7 @@
         <v>46143</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C98" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B98,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A98,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A98,0))</f>
@@ -46241,7 +46270,7 @@
         <v>46143</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C99" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B99,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A99,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A99,0))</f>
@@ -46265,7 +46294,7 @@
         <v>46143</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C100" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B100,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A100,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A100,0))</f>
@@ -46289,7 +46318,7 @@
         <v>46143</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C101" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B101,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A101,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A101,0))</f>
@@ -46313,7 +46342,7 @@
         <v>46143</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C102" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B102,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A102,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A102,0))</f>
@@ -46337,7 +46366,7 @@
         <v>46143</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C103" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B103,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A103,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A103,0))</f>
@@ -46361,7 +46390,7 @@
         <v>46143</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C104" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B104,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A104,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A104,0))</f>
@@ -46385,7 +46414,7 @@
         <v>46143</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C105" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B105,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A105,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A105,0))</f>
@@ -46409,7 +46438,7 @@
         <v>46143</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C106" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B106,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A106,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A106,0))</f>
@@ -46433,7 +46462,7 @@
         <v>46143</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C107" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B107,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A107,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A107,0))</f>
@@ -46457,7 +46486,7 @@
         <v>46143</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C108" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B108,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A108,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A108,0))</f>
@@ -46481,7 +46510,7 @@
         <v>46174</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C109" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B109,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A109,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A109,0))</f>
@@ -46505,7 +46534,7 @@
         <v>46174</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C110" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B110,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A110,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A110,0))</f>
@@ -46529,7 +46558,7 @@
         <v>46174</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C111" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B111,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A111,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A111,0))</f>
@@ -46553,7 +46582,7 @@
         <v>46174</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C112" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B112,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A112,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A112,0))</f>
@@ -46577,7 +46606,7 @@
         <v>46174</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C113" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B113,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A113,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A113,0))</f>
@@ -46601,7 +46630,7 @@
         <v>46174</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C114" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B114,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A114,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A114,0))</f>
@@ -46625,7 +46654,7 @@
         <v>46174</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C115" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B115,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A115,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A115,0))</f>
@@ -46649,7 +46678,7 @@
         <v>46174</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C116" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B116,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A116,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A116,0))</f>
@@ -46673,7 +46702,7 @@
         <v>46174</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C117" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B117,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A117,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A117,0))</f>
@@ -46697,7 +46726,7 @@
         <v>46174</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C118" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B118,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A118,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A118,0))</f>
@@ -46721,7 +46750,7 @@
         <v>46174</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C119" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B119,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A119,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A119,0))</f>
@@ -46745,7 +46774,7 @@
         <v>46204</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C120" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B120,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A120,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A120,0))</f>
@@ -46769,7 +46798,7 @@
         <v>46204</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C121" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B121,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A121,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A121,0))</f>
@@ -46793,7 +46822,7 @@
         <v>46204</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C122" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B122,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A122,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A122,0))</f>
@@ -46817,7 +46846,7 @@
         <v>46204</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C123" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B123,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A123,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A123,0))</f>
@@ -46841,7 +46870,7 @@
         <v>46204</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C124" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B124,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A124,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A124,0))</f>
@@ -46865,7 +46894,7 @@
         <v>46204</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C125" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B125,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A125,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A125,0))</f>
@@ -46889,7 +46918,7 @@
         <v>46204</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C126" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B126,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A126,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A126,0))</f>
@@ -46913,7 +46942,7 @@
         <v>46204</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C127" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B127,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A127,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A127,0))</f>
@@ -46937,7 +46966,7 @@
         <v>46204</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C128" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B128,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A128,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A128,0))</f>
@@ -46961,7 +46990,7 @@
         <v>46204</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C129" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B129,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A129,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A129,0))</f>
@@ -46985,7 +47014,7 @@
         <v>46204</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C130" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B130,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A130,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A130,0))</f>
@@ -47009,7 +47038,7 @@
         <v>46235</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C131" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B131,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A131,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A131,0))</f>
@@ -47033,7 +47062,7 @@
         <v>46235</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C132" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B132,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A132,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A132,0))</f>
@@ -47057,7 +47086,7 @@
         <v>46235</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C133" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B133,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A133,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A133,0))</f>
@@ -47081,7 +47110,7 @@
         <v>46235</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C134" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B134,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A134,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A134,0))</f>
@@ -47105,7 +47134,7 @@
         <v>46235</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C135" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B135,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A135,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A135,0))</f>
@@ -47129,7 +47158,7 @@
         <v>46235</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C136" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B136,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A136,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A136,0))</f>
@@ -47153,7 +47182,7 @@
         <v>46235</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C137" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B137,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A137,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A137,0))</f>
@@ -47177,7 +47206,7 @@
         <v>46235</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C138" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B138,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A138,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A138,0))</f>
@@ -47201,7 +47230,7 @@
         <v>46235</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C139" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B139,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A139,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A139,0))</f>
@@ -47225,7 +47254,7 @@
         <v>46235</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C140" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B140,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A140,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A140,0))</f>
@@ -47249,7 +47278,7 @@
         <v>46235</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C141" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B141,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A141,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A141,0))</f>
@@ -47273,7 +47302,7 @@
         <v>46266</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C142" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B142,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A142,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A142,0))</f>
@@ -47297,7 +47326,7 @@
         <v>46266</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C143" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B143,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A143,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A143,0))</f>
@@ -47321,7 +47350,7 @@
         <v>46266</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C144" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B144,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A144,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A144,0))</f>
@@ -47345,7 +47374,7 @@
         <v>46266</v>
       </c>
       <c r="B145" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C145" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B145,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A145,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A145,0))</f>
@@ -47369,7 +47398,7 @@
         <v>46266</v>
       </c>
       <c r="B146" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C146" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B146,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A146,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A146,0))</f>
@@ -47393,7 +47422,7 @@
         <v>46266</v>
       </c>
       <c r="B147" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C147" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B147,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A147,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A147,0))</f>
@@ -47417,7 +47446,7 @@
         <v>46266</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C148" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B148,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A148,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A148,0))</f>
@@ -47441,7 +47470,7 @@
         <v>46266</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C149" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B149,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A149,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A149,0))</f>
@@ -47465,7 +47494,7 @@
         <v>46266</v>
       </c>
       <c r="B150" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C150" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B150,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A150,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A150,0))</f>
@@ -47489,7 +47518,7 @@
         <v>46266</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C151" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B151,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A151,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A151,0))</f>
@@ -47513,7 +47542,7 @@
         <v>46266</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C152" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B152,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A152,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A152,0))</f>
@@ -47537,7 +47566,7 @@
         <v>46296</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C153" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B153,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A153,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A153,0))</f>
@@ -47561,7 +47590,7 @@
         <v>46296</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C154" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B154,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A154,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A154,0))</f>
@@ -47585,7 +47614,7 @@
         <v>46296</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C155" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B155,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A155,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A155,0))</f>
@@ -47609,7 +47638,7 @@
         <v>46296</v>
       </c>
       <c r="B156" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C156" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B156,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A156,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A156,0))</f>
@@ -47633,7 +47662,7 @@
         <v>46296</v>
       </c>
       <c r="B157" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C157" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B157,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A157,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A157,0))</f>
@@ -47657,7 +47686,7 @@
         <v>46296</v>
       </c>
       <c r="B158" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C158" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B158,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A158,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A158,0))</f>
@@ -47681,7 +47710,7 @@
         <v>46296</v>
       </c>
       <c r="B159" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C159" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B159,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A159,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A159,0))</f>
@@ -47705,7 +47734,7 @@
         <v>46296</v>
       </c>
       <c r="B160" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C160" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B160,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A160,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A160,0))</f>
@@ -47729,7 +47758,7 @@
         <v>46296</v>
       </c>
       <c r="B161" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C161" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B161,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A161,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A161,0))</f>
@@ -47753,7 +47782,7 @@
         <v>46296</v>
       </c>
       <c r="B162" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C162" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B162,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A162,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A162,0))</f>
@@ -47777,7 +47806,7 @@
         <v>46296</v>
       </c>
       <c r="B163" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C163" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B163,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A163,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A163,0))</f>
@@ -47801,7 +47830,7 @@
         <v>46327</v>
       </c>
       <c r="B164" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C164" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B164,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A164,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A164,0))</f>
@@ -47825,7 +47854,7 @@
         <v>46327</v>
       </c>
       <c r="B165" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C165" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B165,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A165,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A165,0))</f>
@@ -47849,7 +47878,7 @@
         <v>46327</v>
       </c>
       <c r="B166" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C166" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B166,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A166,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A166,0))</f>
@@ -47873,7 +47902,7 @@
         <v>46327</v>
       </c>
       <c r="B167" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C167" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B167,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A167,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A167,0))</f>
@@ -47897,7 +47926,7 @@
         <v>46327</v>
       </c>
       <c r="B168" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C168" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B168,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A168,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A168,0))</f>
@@ -47921,7 +47950,7 @@
         <v>46327</v>
       </c>
       <c r="B169" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C169" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B169,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A169,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A169,0))</f>
@@ -47945,7 +47974,7 @@
         <v>46327</v>
       </c>
       <c r="B170" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C170" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B170,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A170,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A170,0))</f>
@@ -47969,7 +47998,7 @@
         <v>46327</v>
       </c>
       <c r="B171" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C171" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B171,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A171,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A171,0))</f>
@@ -47993,7 +48022,7 @@
         <v>46327</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C172" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B172,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A172,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A172,0))</f>
@@ -48017,7 +48046,7 @@
         <v>46327</v>
       </c>
       <c r="B173" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C173" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B173,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A173,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A173,0))</f>
@@ -48041,7 +48070,7 @@
         <v>46327</v>
       </c>
       <c r="B174" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C174" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B174,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A174,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A174,0))</f>
@@ -48065,7 +48094,7 @@
         <v>46357</v>
       </c>
       <c r="B175" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C175" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B175,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A175,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A175,0))</f>
@@ -48089,7 +48118,7 @@
         <v>46357</v>
       </c>
       <c r="B176" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C176" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B176,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A176,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A176,0))</f>
@@ -48113,7 +48142,7 @@
         <v>46357</v>
       </c>
       <c r="B177" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C177" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B177,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A177,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A177,0))</f>
@@ -48137,7 +48166,7 @@
         <v>46357</v>
       </c>
       <c r="B178" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C178" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B178,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A178,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A178,0))</f>
@@ -48161,7 +48190,7 @@
         <v>46357</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C179" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B179,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A179,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A179,0))</f>
@@ -48185,7 +48214,7 @@
         <v>46357</v>
       </c>
       <c r="B180" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C180" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B180,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A180,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A180,0))</f>
@@ -48209,7 +48238,7 @@
         <v>46357</v>
       </c>
       <c r="B181" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C181" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B181,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A181,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A181,0))</f>
@@ -48233,7 +48262,7 @@
         <v>46357</v>
       </c>
       <c r="B182" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C182" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B182,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A182,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A182,0))</f>
@@ -48257,7 +48286,7 @@
         <v>46357</v>
       </c>
       <c r="B183" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C183" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B183,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A183,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A183,0))</f>
@@ -48281,7 +48310,7 @@
         <v>46357</v>
       </c>
       <c r="B184" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C184" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B184,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A184,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A184,0))</f>
@@ -48305,7 +48334,7 @@
         <v>46357</v>
       </c>
       <c r="B185" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C185" s="19" t="n">
         <f aca="false">SUMIFS('Technician Daily'!$C$3:$C$3001,'Technician Daily'!$B$3:$B$3001,$B185,'Technician Daily'!$A$3:$A$3001,"&gt;="&amp;$A185,'Technician Daily'!$A$3:$A$3001,"&lt;="&amp;EOMONTH($A185,0))</f>
